--- a/EXCEL/class notes/day14 chart&subtotal&text fn/Text Functions.xlsx
+++ b/EXCEL/class notes/day14 chart&subtotal&text fn/Text Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day14 chart&amp;subtotal&amp;text fn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20C43B0-2C5E-4239-BF2D-3287E8AD907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14375FF8-47DB-47B0-85AE-B3388091E61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="1" activeTab="6" xr2:uid="{26FBDAB0-4734-43EF-B107-95B14C5BBF0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="867" firstSheet="1" activeTab="6" xr2:uid="{26FBDAB0-4734-43EF-B107-95B14C5BBF0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Text - Merge" sheetId="10" r:id="rId1"/>
@@ -25,6 +25,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -713,7 +722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -733,7 +742,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2232,19 +2240,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93547CF-EADA-4C41-B8B6-6DEB556CF001}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="10.1875" customWidth="1"/>
-    <col min="4" max="4" width="15.8125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.2109375" customWidth="1"/>
+    <col min="4" max="4" width="15.78515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>29</v>
       </c>
@@ -2270,7 +2278,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
@@ -2320,7 +2328,7 @@
         <v>MR.VihaanKumar</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>MR.VijayKhanna</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -2388,7 +2396,7 @@
         <v>MR.JohnTORRES</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2422,7 +2430,7 @@
         <v>MS.JosephZHU</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2456,7 +2464,7 @@
         <v>MRS.ELIZABETHJOHNSON</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2490,7 +2498,7 @@
         <v>MR.JULIORUIZ</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2524,7 +2532,7 @@
         <v>MR.MARCOMEHTA</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -2558,7 +2566,7 @@
         <v>MRS.ROBINVERHOFF</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2592,7 +2600,7 @@
         <v>MR.SHANNONCARLSON</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -2638,19 +2646,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE38F8E-EDFB-4E4A-B198-59C12D1C4093}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="37.5625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.3125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.78515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
@@ -2661,7 +2669,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
@@ -2693,7 +2701,7 @@
         <v>Maharashtra</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>42</v>
       </c>
@@ -2725,7 +2733,7 @@
         <v>Maharashtra</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -2741,7 +2749,7 @@
       <c r="G4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>82</v>
       </c>
       <c r="J4" s="2" t="str">
@@ -2757,7 +2765,7 @@
         <v>Uttar Pradesh</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -2789,7 +2797,7 @@
         <v>Odisha</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2821,7 +2829,7 @@
         <v>Maharashtra</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -2848,12 +2856,12 @@
         <f t="shared" si="0"/>
         <v>Dehradun</v>
       </c>
-      <c r="L7" s="20" t="str">
+      <c r="L7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Uttarakhand</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -2885,7 +2893,7 @@
         <v>Gujarat</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2917,7 +2925,7 @@
         <v>Rajasthan</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -2949,7 +2957,7 @@
         <v>Madhya Pradesh</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>0</v>
       </c>
@@ -2981,12 +2989,12 @@
         <v>Andhra Pradesh</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="D14" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>105</v>
       </c>
@@ -2994,7 +3002,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
         <v>106</v>
       </c>
@@ -3002,7 +3010,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.5">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
         <v>107</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.5">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
         <v>108</v>
       </c>
@@ -3018,7 +3026,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.5">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
         <v>109</v>
       </c>
@@ -3038,13 +3046,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BD5A9A-1FD7-48D5-8A05-707DDBDCDEA1}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="10.1875" customWidth="1"/>
+    <col min="3" max="3" width="10.2109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>29</v>
       </c>
@@ -3055,7 +3063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3102,7 +3110,7 @@
         <v>Kumar</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -3149,7 +3157,7 @@
         <v>Lalwani</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3196,7 +3204,7 @@
         <v>Badanaa</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3243,7 +3251,7 @@
         <v>Zhuaan</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3290,7 +3298,7 @@
         <v>Johnson</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -3337,7 +3345,7 @@
         <v>Ruiz</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3384,7 +3392,7 @@
         <v>Mehtaji</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -3431,7 +3439,7 @@
         <v>Verhoff</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -3478,7 +3486,7 @@
         <v>Pooja</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -3537,13 +3545,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4702809-037C-421A-B370-C53F32A96B37}">
   <dimension ref="B1:H11"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
@@ -3554,7 +3562,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
@@ -3573,7 +3581,7 @@
         <v>Age is 26 Years</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
@@ -3592,7 +3600,7 @@
         <v>Age is 26 Years</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
@@ -3611,7 +3619,7 @@
         <v>Age is 30 Years</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -3630,7 +3638,7 @@
         <v>Age is 22 Years</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
@@ -3649,7 +3657,7 @@
         <v>Age is 15 Years</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
@@ -3668,7 +3676,7 @@
         <v>Age is 22 Years</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
@@ -3687,7 +3695,7 @@
         <v>Age is 34 Years</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3706,7 +3714,7 @@
         <v>Age is 29 Years</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
@@ -3725,7 +3733,7 @@
         <v>Age is 19 Years</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
@@ -3755,20 +3763,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4334C3E1-3E28-46A3-A37B-DF1286451A40}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="23.6875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.4375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.4375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -3785,7 +3793,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
@@ -3802,7 +3810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -3819,7 +3827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -3836,7 +3844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -3853,7 +3861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -3870,7 +3878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -3887,7 +3895,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -3904,7 +3912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -3921,7 +3929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
@@ -3952,14 +3960,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D82AC76-C1D5-475F-B891-0CF75FBE363E}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.1875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.2109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>54</v>
       </c>
@@ -3967,7 +3975,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>55</v>
       </c>
@@ -3993,7 +4001,7 @@
         <v>152156</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -4019,7 +4027,7 @@
         <v>152156</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>56</v>
       </c>
@@ -4045,7 +4053,7 @@
         <v>138688</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>57</v>
       </c>
@@ -4071,7 +4079,7 @@
         <v>108966</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
@@ -4097,7 +4105,7 @@
         <v>108966</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
@@ -4123,7 +4131,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -4149,7 +4157,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -4175,7 +4183,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>58</v>
       </c>
@@ -4201,7 +4209,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>58</v>
       </c>
@@ -4227,7 +4235,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
@@ -4241,7 +4249,7 @@
         <v>152156</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -4255,7 +4263,7 @@
         <v>152156</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -4269,7 +4277,7 @@
         <v>138688</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>57</v>
       </c>
@@ -4283,7 +4291,7 @@
         <v>108966</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -4297,7 +4305,7 @@
         <v>108966</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>58</v>
       </c>
@@ -4311,7 +4319,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
@@ -4325,7 +4333,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>58</v>
       </c>
@@ -4339,7 +4347,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>58</v>
       </c>
@@ -4353,7 +4361,7 @@
         <v>115812</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>58</v>
       </c>
@@ -4379,14 +4387,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D85124-5909-4839-BD6F-153EC9BEF0D5}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="10.1875" customWidth="1"/>
+    <col min="2" max="2" width="10.2109375" customWidth="1"/>
     <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
@@ -4403,7 +4411,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -4424,7 +4432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -4442,7 +4450,7 @@
         <v>Mrs</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -4460,7 +4468,7 @@
         <v>Ms</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -4478,7 +4486,7 @@
         <v>Mrs</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -4496,7 +4504,7 @@
         <v>Mr</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -4514,7 +4522,7 @@
         <v>Mr</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -4532,7 +4540,7 @@
         <v>Mr</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
@@ -4550,7 +4558,7 @@
         <v>Mr</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -4568,7 +4576,7 @@
         <v>Mr</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
